--- a/artfynd/A 34231-2024 artfynd.xlsx
+++ b/artfynd/A 34231-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>126167896</v>
       </c>
       <c r="B2" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -778,6 +778,1294 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126199077</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98362</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Korrissjön, Korrissjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>484589</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6839395</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126200800</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98258</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Strumpberget, Strumpberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>484404</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6839142</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126199169</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98258</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Strumpberget, Strumpberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>484432</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6839494</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126200419</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98362</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Strumpberget, Strumpberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>484380</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6839287</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126200436</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98362</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Korrissjön, Korrissjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>484367</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6839266</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126200252</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Strumpberget, Strumpberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>484364</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6839315</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126200719</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98245</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Strumpberget, Strumpberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>484370</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6839140</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126200472</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98258</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Strumpberget, Strumpberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>484365</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6839266</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126199156</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98258</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Strumpberget, Strumpberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>484446</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6839490</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126199878</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Korrissjön, Korrissjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>484333</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6839547</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126200489</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98245</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Strumpberget, Strumpberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>484383</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6839247</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126200382</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98245</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Korrissjön, Korrissjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>484371</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6839289</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126198918</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98362</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Strumpberget, Strumpberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>484465</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6839293</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34231-2024 artfynd.xlsx
+++ b/artfynd/A 34231-2024 artfynd.xlsx
@@ -1760,7 +1760,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126200489</v>
+        <v>126200382</v>
       </c>
       <c r="B13" t="n">
         <v>98245</v>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1800,14 +1800,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Strumpberget, Strumpberget, Dlr</t>
+          <t>Korrissjön, Korrissjön, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>484383</v>
+        <v>484371</v>
       </c>
       <c r="R13" t="n">
-        <v>6839247</v>
+        <v>6839289</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1866,7 +1866,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126200382</v>
+        <v>126200489</v>
       </c>
       <c r="B14" t="n">
         <v>98245</v>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1906,14 +1906,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Korrissjön, Korrissjön, Dlr</t>
+          <t>Strumpberget, Strumpberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484371</v>
+        <v>484383</v>
       </c>
       <c r="R14" t="n">
-        <v>6839289</v>
+        <v>6839247</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 34231-2024 artfynd.xlsx
+++ b/artfynd/A 34231-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126167896</v>
       </c>
       <c r="B2" t="n">
-        <v>98259</v>
+        <v>98261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126199077</v>
       </c>
       <c r="B3" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>126200800</v>
       </c>
       <c r="B4" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>126199169</v>
       </c>
       <c r="B5" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>126200419</v>
       </c>
       <c r="B6" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>126200436</v>
       </c>
       <c r="B7" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>126200719</v>
       </c>
       <c r="B9" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>126200472</v>
       </c>
       <c r="B10" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,48 +1566,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126199156</v>
+        <v>126199878</v>
       </c>
       <c r="B11" t="n">
-        <v>98258</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Strumpberget, Strumpberget, Dlr</t>
+          <t>Korrissjön, Korrissjön, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484446</v>
+        <v>484333</v>
       </c>
       <c r="R11" t="n">
-        <v>6839490</v>
+        <v>6839547</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1651,60 +1651,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126199878</v>
+        <v>126199156</v>
       </c>
       <c r="B12" t="n">
-        <v>78973</v>
+        <v>98260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Korrissjön, Korrissjön, Dlr</t>
+          <t>Strumpberget, Strumpberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484333</v>
+        <v>484446</v>
       </c>
       <c r="R12" t="n">
-        <v>6839547</v>
+        <v>6839490</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1748,22 +1748,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126200382</v>
+        <v>126200489</v>
       </c>
       <c r="B13" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1800,14 +1800,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Korrissjön, Korrissjön, Dlr</t>
+          <t>Strumpberget, Strumpberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>484371</v>
+        <v>484383</v>
       </c>
       <c r="R13" t="n">
-        <v>6839289</v>
+        <v>6839247</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1866,10 +1866,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126200489</v>
+        <v>126200382</v>
       </c>
       <c r="B14" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1906,14 +1906,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Strumpberget, Strumpberget, Dlr</t>
+          <t>Korrissjön, Korrissjön, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484383</v>
+        <v>484371</v>
       </c>
       <c r="R14" t="n">
-        <v>6839247</v>
+        <v>6839289</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1975,7 +1975,7 @@
         <v>126198918</v>
       </c>
       <c r="B15" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34231-2024 artfynd.xlsx
+++ b/artfynd/A 34231-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126167896</v>
       </c>
       <c r="B2" t="n">
-        <v>98261</v>
+        <v>98263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126199077</v>
       </c>
       <c r="B3" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>126200800</v>
       </c>
       <c r="B4" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>126199169</v>
       </c>
       <c r="B5" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>126200419</v>
       </c>
       <c r="B6" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>126200436</v>
       </c>
       <c r="B7" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>126200719</v>
       </c>
       <c r="B9" t="n">
-        <v>98247</v>
+        <v>98249</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>126200472</v>
       </c>
       <c r="B10" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>126199156</v>
       </c>
       <c r="B12" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>126200489</v>
       </c>
       <c r="B13" t="n">
-        <v>98247</v>
+        <v>98249</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>126200382</v>
       </c>
       <c r="B14" t="n">
-        <v>98247</v>
+        <v>98249</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>126198918</v>
       </c>
       <c r="B15" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34231-2024 artfynd.xlsx
+++ b/artfynd/A 34231-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126167896</v>
       </c>
       <c r="B2" t="n">
-        <v>98263</v>
+        <v>98267</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126199077</v>
       </c>
       <c r="B3" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>126200800</v>
       </c>
       <c r="B4" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>126199169</v>
       </c>
       <c r="B5" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>126200419</v>
       </c>
       <c r="B6" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>126200436</v>
       </c>
       <c r="B7" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>126200252</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>126200719</v>
       </c>
       <c r="B9" t="n">
-        <v>98249</v>
+        <v>98253</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>126200472</v>
       </c>
       <c r="B10" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,48 +1566,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126199878</v>
+        <v>126199156</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>98266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Korrissjön, Korrissjön, Dlr</t>
+          <t>Strumpberget, Strumpberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484333</v>
+        <v>484446</v>
       </c>
       <c r="R11" t="n">
-        <v>6839547</v>
+        <v>6839490</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1651,60 +1651,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126199156</v>
+        <v>126199878</v>
       </c>
       <c r="B12" t="n">
-        <v>98262</v>
+        <v>78977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Strumpberget, Strumpberget, Dlr</t>
+          <t>Korrissjön, Korrissjön, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484446</v>
+        <v>484333</v>
       </c>
       <c r="R12" t="n">
-        <v>6839490</v>
+        <v>6839547</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1748,12 +1748,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1763,7 +1763,7 @@
         <v>126200489</v>
       </c>
       <c r="B13" t="n">
-        <v>98249</v>
+        <v>98253</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>126200382</v>
       </c>
       <c r="B14" t="n">
-        <v>98249</v>
+        <v>98253</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>126198918</v>
       </c>
       <c r="B15" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34231-2024 artfynd.xlsx
+++ b/artfynd/A 34231-2024 artfynd.xlsx
@@ -1566,48 +1566,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126199156</v>
+        <v>126199878</v>
       </c>
       <c r="B11" t="n">
-        <v>98266</v>
+        <v>78977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Strumpberget, Strumpberget, Dlr</t>
+          <t>Korrissjön, Korrissjön, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484446</v>
+        <v>484333</v>
       </c>
       <c r="R11" t="n">
-        <v>6839490</v>
+        <v>6839547</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1651,60 +1651,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126199878</v>
+        <v>126199156</v>
       </c>
       <c r="B12" t="n">
-        <v>78977</v>
+        <v>98266</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Korrissjön, Korrissjön, Dlr</t>
+          <t>Strumpberget, Strumpberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484333</v>
+        <v>484446</v>
       </c>
       <c r="R12" t="n">
-        <v>6839547</v>
+        <v>6839490</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1748,12 +1748,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 34231-2024 artfynd.xlsx
+++ b/artfynd/A 34231-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126167896</v>
       </c>
       <c r="B2" t="n">
-        <v>98267</v>
+        <v>98270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126199077</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>126200800</v>
       </c>
       <c r="B4" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>126199169</v>
       </c>
       <c r="B5" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>126200419</v>
       </c>
       <c r="B6" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>126200436</v>
       </c>
       <c r="B7" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>126200719</v>
       </c>
       <c r="B9" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>126200472</v>
       </c>
       <c r="B10" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>126199156</v>
       </c>
       <c r="B12" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>126200489</v>
       </c>
       <c r="B13" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>126200382</v>
       </c>
       <c r="B14" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>126198918</v>
       </c>
       <c r="B15" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34231-2024 artfynd.xlsx
+++ b/artfynd/A 34231-2024 artfynd.xlsx
@@ -1566,48 +1566,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126199878</v>
+        <v>126199156</v>
       </c>
       <c r="B11" t="n">
-        <v>78977</v>
+        <v>98269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Korrissjön, Korrissjön, Dlr</t>
+          <t>Strumpberget, Strumpberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484333</v>
+        <v>484446</v>
       </c>
       <c r="R11" t="n">
-        <v>6839547</v>
+        <v>6839490</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1651,60 +1651,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126199156</v>
+        <v>126199878</v>
       </c>
       <c r="B12" t="n">
-        <v>98269</v>
+        <v>78977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Strumpberget, Strumpberget, Dlr</t>
+          <t>Korrissjön, Korrissjön, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484446</v>
+        <v>484333</v>
       </c>
       <c r="R12" t="n">
-        <v>6839490</v>
+        <v>6839547</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1748,12 +1748,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 34231-2024 artfynd.xlsx
+++ b/artfynd/A 34231-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126167896</v>
       </c>
       <c r="B2" t="n">
-        <v>98270</v>
+        <v>98279</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126199077</v>
       </c>
       <c r="B3" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>126200800</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>126199169</v>
       </c>
       <c r="B5" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>126200419</v>
       </c>
       <c r="B6" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>126200436</v>
       </c>
       <c r="B7" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>126200252</v>
       </c>
       <c r="B8" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>126200719</v>
       </c>
       <c r="B9" t="n">
-        <v>98256</v>
+        <v>98265</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>126200472</v>
       </c>
       <c r="B10" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,48 +1566,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126199156</v>
+        <v>126199878</v>
       </c>
       <c r="B11" t="n">
-        <v>98269</v>
+        <v>78980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Strumpberget, Strumpberget, Dlr</t>
+          <t>Korrissjön, Korrissjön, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484446</v>
+        <v>484333</v>
       </c>
       <c r="R11" t="n">
-        <v>6839490</v>
+        <v>6839547</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1651,60 +1651,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126199878</v>
+        <v>126199156</v>
       </c>
       <c r="B12" t="n">
-        <v>78977</v>
+        <v>98278</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Korrissjön, Korrissjön, Dlr</t>
+          <t>Strumpberget, Strumpberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484333</v>
+        <v>484446</v>
       </c>
       <c r="R12" t="n">
-        <v>6839547</v>
+        <v>6839490</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1748,12 +1748,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1763,7 +1763,7 @@
         <v>126200489</v>
       </c>
       <c r="B13" t="n">
-        <v>98256</v>
+        <v>98265</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>126200382</v>
       </c>
       <c r="B14" t="n">
-        <v>98256</v>
+        <v>98265</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>126198918</v>
       </c>
       <c r="B15" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34231-2024 artfynd.xlsx
+++ b/artfynd/A 34231-2024 artfynd.xlsx
@@ -1275,32 +1275,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126200252</v>
+        <v>126200719</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>98265</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1310,13 +1310,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484364</v>
+        <v>484370</v>
       </c>
       <c r="R8" t="n">
-        <v>6839315</v>
+        <v>6839140</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1360,44 +1360,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126200719</v>
+        <v>126200252</v>
       </c>
       <c r="B9" t="n">
-        <v>98265</v>
+        <v>78980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1407,13 +1407,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484370</v>
+        <v>484364</v>
       </c>
       <c r="R9" t="n">
-        <v>6839140</v>
+        <v>6839315</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 34231-2024 artfynd.xlsx
+++ b/artfynd/A 34231-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126167896</v>
+        <v>126199878</v>
       </c>
       <c r="B2" t="n">
-        <v>98279</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223591</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mårten-Olsasmyrtäkten, Mårten-Olsasmyrtäkten, Dlr</t>
+          <t>Korrissjön, Korrissjön, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484454</v>
+        <v>484333</v>
       </c>
       <c r="R2" t="n">
-        <v>6839484</v>
+        <v>6839547</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,60 +760,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126199077</v>
+        <v>126200252</v>
       </c>
       <c r="B3" t="n">
-        <v>98382</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Korrissjön, Korrissjön, Dlr</t>
+          <t>Strumpberget, Strumpberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484589</v>
+        <v>484364</v>
       </c>
       <c r="R3" t="n">
-        <v>6839395</v>
+        <v>6839315</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126200800</v>
+        <v>126200566</v>
       </c>
       <c r="B4" t="n">
-        <v>98278</v>
+        <v>99026</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,16 +880,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>219788</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -906,17 +897,26 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Strumpberget, Strumpberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484404</v>
+        <v>484347</v>
       </c>
       <c r="R4" t="n">
-        <v>6839142</v>
+        <v>6839203</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,22 +963,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126199169</v>
+        <v>126200717</v>
       </c>
       <c r="B5" t="n">
-        <v>98278</v>
+        <v>99026</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,16 +986,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>219788</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1003,29 +1003,20 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Strumpberget, Strumpberget, Dlr</t>
+          <t>Korrissjön, Korrissjön, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484432</v>
+        <v>484353</v>
       </c>
       <c r="R5" t="n">
-        <v>6839494</v>
+        <v>6839119</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126200419</v>
+        <v>126199156</v>
       </c>
       <c r="B6" t="n">
-        <v>98382</v>
+        <v>99035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1092,21 +1083,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1116,13 +1107,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484380</v>
+        <v>484446</v>
       </c>
       <c r="R6" t="n">
-        <v>6839287</v>
+        <v>6839490</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,10 +1169,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126200436</v>
+        <v>126199169</v>
       </c>
       <c r="B7" t="n">
-        <v>98382</v>
+        <v>99035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,34 +1180,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Korrissjön, Korrissjön, Dlr</t>
+          <t>Strumpberget, Strumpberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484367</v>
+        <v>484432</v>
       </c>
       <c r="R7" t="n">
-        <v>6839266</v>
+        <v>6839494</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1263,44 +1263,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126200252</v>
+        <v>126200472</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>99035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484364</v>
+        <v>484365</v>
       </c>
       <c r="R8" t="n">
-        <v>6839315</v>
+        <v>6839266</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126200719</v>
+        <v>126200553</v>
       </c>
       <c r="B9" t="n">
-        <v>98265</v>
+        <v>99035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1407,13 +1407,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484370</v>
+        <v>484328</v>
       </c>
       <c r="R9" t="n">
-        <v>6839140</v>
+        <v>6839224</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126200472</v>
+        <v>126200575</v>
       </c>
       <c r="B10" t="n">
-        <v>98278</v>
+        <v>99035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1504,13 +1504,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484365</v>
+        <v>484351</v>
       </c>
       <c r="R10" t="n">
-        <v>6839266</v>
+        <v>6839206</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1566,45 +1566,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126199878</v>
+        <v>126200800</v>
       </c>
       <c r="B11" t="n">
-        <v>78980</v>
+        <v>99035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Korrissjön, Korrissjön, Dlr</t>
+          <t>Strumpberget, Strumpberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484333</v>
+        <v>484404</v>
       </c>
       <c r="R11" t="n">
-        <v>6839547</v>
+        <v>6839142</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126199156</v>
+        <v>126200382</v>
       </c>
       <c r="B12" t="n">
-        <v>98278</v>
+        <v>99022</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1674,37 +1674,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>220093</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Strumpberget, Strumpberget, Dlr</t>
+          <t>Korrissjön, Korrissjön, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484446</v>
+        <v>484371</v>
       </c>
       <c r="R12" t="n">
-        <v>6839490</v>
+        <v>6839289</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1748,12 +1757,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1763,7 +1772,7 @@
         <v>126200489</v>
       </c>
       <c r="B13" t="n">
-        <v>98265</v>
+        <v>99022</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1866,10 +1875,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126200382</v>
+        <v>126200719</v>
       </c>
       <c r="B14" t="n">
-        <v>98265</v>
+        <v>99022</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1894,29 +1903,20 @@
           <t>Châtel.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Korrissjön, Korrissjön, Dlr</t>
+          <t>Strumpberget, Strumpberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484371</v>
+        <v>484370</v>
       </c>
       <c r="R14" t="n">
-        <v>6839289</v>
+        <v>6839140</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>126198918</v>
       </c>
       <c r="B15" t="n">
-        <v>98382</v>
+        <v>99140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2066,6 +2066,500 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126199077</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Korrissjön, Korrissjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>484589</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6839395</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126200419</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Strumpberget, Strumpberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>484380</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6839287</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126200436</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Korrissjön, Korrissjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>484367</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6839266</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126200538</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Strumpberget, Strumpberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>484349</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6839224</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126167896</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mårten-Olsasmyrtäkten, Mårten-Olsasmyrtäkten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>484454</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6839484</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
